--- a/doc/TestDoc/Test Suite/TestPlanPrincipleController.xlsx
+++ b/doc/TestDoc/Test Suite/TestPlanPrincipleController.xlsx
@@ -23,9 +23,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="7">
     <font>
       <name val="Aptos Narrow"/>
@@ -331,7 +329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -454,6 +452,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1356,7 +1356,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B30" s="41" t="n"/>
+      <c r="B30" s="50" t="n"/>
       <c r="C30" s="39" t="n">
         <v>28</v>
       </c>
@@ -1388,7 +1388,6 @@
     <col width="8.21875" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
     <col width="13.21875" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
     <col width="34.44140625" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
-    <col width="8.88671875" customWidth="1" style="2" min="8" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1494,7 +1493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H20"/>
+  <dimension ref="A3:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1504,7 +1503,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -1518,12 +1516,11 @@
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="41" t="n"/>
-      <c r="D3" s="41" t="n"/>
-      <c r="E3" s="41" t="n"/>
-      <c r="F3" s="41" t="n"/>
-      <c r="G3" s="41" t="n"/>
-      <c r="H3" s="41" t="n"/>
+      <c r="C3" s="51" t="n"/>
+      <c r="D3" s="51" t="n"/>
+      <c r="E3" s="51" t="n"/>
+      <c r="F3" s="51" t="n"/>
+      <c r="G3" s="50" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="42" t="inlineStr">
@@ -1536,12 +1533,11 @@
           <t>GameController</t>
         </is>
       </c>
-      <c r="C4" s="41" t="n"/>
-      <c r="D4" s="41" t="n"/>
-      <c r="E4" s="41" t="n"/>
-      <c r="F4" s="41" t="n"/>
-      <c r="G4" s="41" t="n"/>
-      <c r="H4" s="41" t="n"/>
+      <c r="C4" s="51" t="n"/>
+      <c r="D4" s="51" t="n"/>
+      <c r="E4" s="51" t="n"/>
+      <c r="F4" s="51" t="n"/>
+      <c r="G4" s="50" t="n"/>
     </row>
     <row r="5" ht="35.4" customHeight="1">
       <c r="A5" s="42" t="inlineStr">
@@ -1554,12 +1550,11 @@
           <t>Window 11, java version "1.8.0_503" , Junit 5</t>
         </is>
       </c>
-      <c r="C5" s="41" t="n"/>
-      <c r="D5" s="41" t="n"/>
-      <c r="E5" s="41" t="n"/>
-      <c r="F5" s="41" t="n"/>
-      <c r="G5" s="41" t="n"/>
-      <c r="H5" s="41" t="n"/>
+      <c r="C5" s="51" t="n"/>
+      <c r="D5" s="51" t="n"/>
+      <c r="E5" s="51" t="n"/>
+      <c r="F5" s="51" t="n"/>
+      <c r="G5" s="50" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="42" t="inlineStr">
@@ -1570,12 +1565,11 @@
       <c r="B6" s="45" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="41" t="n"/>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="41" t="n"/>
-      <c r="F6" s="41" t="n"/>
-      <c r="G6" s="41" t="n"/>
-      <c r="H6" s="41" t="n"/>
+      <c r="C6" s="51" t="n"/>
+      <c r="D6" s="51" t="n"/>
+      <c r="E6" s="51" t="n"/>
+      <c r="F6" s="51" t="n"/>
+      <c r="G6" s="50" t="n"/>
     </row>
     <row r="7" ht="35.4" customHeight="1">
       <c r="A7" s="42" t="inlineStr">
@@ -1588,12 +1582,11 @@
           <t>Mock GameService; @Test methods call the controller directly</t>
         </is>
       </c>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="41" t="n"/>
-      <c r="F7" s="41" t="n"/>
-      <c r="G7" s="41" t="n"/>
-      <c r="H7" s="41" t="n"/>
+      <c r="C7" s="51" t="n"/>
+      <c r="D7" s="51" t="n"/>
+      <c r="E7" s="51" t="n"/>
+      <c r="F7" s="51" t="n"/>
+      <c r="G7" s="50" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="43" t="inlineStr">
@@ -1656,7 +1649,6 @@
       <c r="E12" s="43" t="n"/>
       <c r="F12" s="43" t="n"/>
       <c r="G12" s="43" t="n"/>
-      <c r="H12" s="48" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="43" t="inlineStr">
@@ -1682,7 +1674,6 @@
       <c r="E13" s="43" t="n"/>
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="43" t="n"/>
-      <c r="H13" s="48" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="43" t="inlineStr">
@@ -1708,11 +1699,6 @@
       <c r="E14" s="43" t="n"/>
       <c r="F14" s="43" t="n"/>
       <c r="G14" s="43" t="n"/>
-      <c r="H14" s="48" t="inlineStr">
-        <is>
-          <t>GET /api/games/{gameId}, GameController.java:39</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="43" t="inlineStr">
@@ -1738,11 +1724,6 @@
       <c r="E15" s="43" t="n"/>
       <c r="F15" s="43" t="n"/>
       <c r="G15" s="43" t="n"/>
-      <c r="H15" s="48" t="inlineStr">
-        <is>
-          <t>GET /api/games/code/{roomCode}, GameController.java:44</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="43" t="inlineStr">
@@ -1768,11 +1749,6 @@
       <c r="E16" s="43" t="n"/>
       <c r="F16" s="43" t="n"/>
       <c r="G16" s="43" t="n"/>
-      <c r="H16" s="48" t="inlineStr">
-        <is>
-          <t>confirm the exception handler mapping</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="43" t="inlineStr">
@@ -1798,11 +1774,6 @@
       <c r="E17" s="43" t="n"/>
       <c r="F17" s="43" t="n"/>
       <c r="G17" s="43" t="n"/>
-      <c r="H17" s="48" t="inlineStr">
-        <is>
-          <t>GameController.java:49</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="43" t="inlineStr">
@@ -1828,11 +1799,6 @@
       <c r="E18" s="43" t="n"/>
       <c r="F18" s="43" t="n"/>
       <c r="G18" s="43" t="n"/>
-      <c r="H18" s="48" t="inlineStr">
-        <is>
-          <t>GameController.java:55</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="43" t="inlineStr">
@@ -1858,11 +1824,6 @@
       <c r="E19" s="43" t="n"/>
       <c r="F19" s="43" t="n"/>
       <c r="G19" s="43" t="n"/>
-      <c r="H19" s="48" t="inlineStr">
-        <is>
-          <t>GameController.java:34</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="43" t="inlineStr">
@@ -1888,11 +1849,6 @@
       <c r="E20" s="43" t="n"/>
       <c r="F20" s="43" t="n"/>
       <c r="G20" s="43" t="n"/>
-      <c r="H20" s="48" t="inlineStr">
-        <is>
-          <t>GET /api/games/{gameId}/snapshot, GameController.java:68</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1912,7 +1868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H17"/>
+  <dimension ref="A3:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1922,7 +1878,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -1936,12 +1891,11 @@
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="41" t="n"/>
-      <c r="D3" s="41" t="n"/>
-      <c r="E3" s="41" t="n"/>
-      <c r="F3" s="41" t="n"/>
-      <c r="G3" s="41" t="n"/>
-      <c r="H3" s="41" t="n"/>
+      <c r="C3" s="51" t="n"/>
+      <c r="D3" s="51" t="n"/>
+      <c r="E3" s="51" t="n"/>
+      <c r="F3" s="51" t="n"/>
+      <c r="G3" s="50" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="42" t="inlineStr">
@@ -1954,12 +1908,11 @@
           <t>GameEndpoint</t>
         </is>
       </c>
-      <c r="C4" s="41" t="n"/>
-      <c r="D4" s="41" t="n"/>
-      <c r="E4" s="41" t="n"/>
-      <c r="F4" s="41" t="n"/>
-      <c r="G4" s="41" t="n"/>
-      <c r="H4" s="41" t="n"/>
+      <c r="C4" s="51" t="n"/>
+      <c r="D4" s="51" t="n"/>
+      <c r="E4" s="51" t="n"/>
+      <c r="F4" s="51" t="n"/>
+      <c r="G4" s="50" t="n"/>
     </row>
     <row r="5" ht="35.4" customHeight="1">
       <c r="A5" s="42" t="inlineStr">
@@ -1972,12 +1925,11 @@
           <t>Window 11, java version "1.8.0_503" , Junit 5</t>
         </is>
       </c>
-      <c r="C5" s="41" t="n"/>
-      <c r="D5" s="41" t="n"/>
-      <c r="E5" s="41" t="n"/>
-      <c r="F5" s="41" t="n"/>
-      <c r="G5" s="41" t="n"/>
-      <c r="H5" s="41" t="n"/>
+      <c r="C5" s="51" t="n"/>
+      <c r="D5" s="51" t="n"/>
+      <c r="E5" s="51" t="n"/>
+      <c r="F5" s="51" t="n"/>
+      <c r="G5" s="50" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="42" t="inlineStr">
@@ -1988,12 +1940,11 @@
       <c r="B6" s="45" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="41" t="n"/>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="41" t="n"/>
-      <c r="F6" s="41" t="n"/>
-      <c r="G6" s="41" t="n"/>
-      <c r="H6" s="41" t="n"/>
+      <c r="C6" s="51" t="n"/>
+      <c r="D6" s="51" t="n"/>
+      <c r="E6" s="51" t="n"/>
+      <c r="F6" s="51" t="n"/>
+      <c r="G6" s="50" t="n"/>
     </row>
     <row r="7" ht="35.4" customHeight="1">
       <c r="A7" s="42" t="inlineStr">
@@ -2006,12 +1957,11 @@
           <t>@WebMvcTest(GameController, PlayerController, TurnController, MarshalDraftController, GameLogController) with @MockBean services</t>
         </is>
       </c>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="41" t="n"/>
-      <c r="F7" s="41" t="n"/>
-      <c r="G7" s="41" t="n"/>
-      <c r="H7" s="41" t="n"/>
+      <c r="C7" s="51" t="n"/>
+      <c r="D7" s="51" t="n"/>
+      <c r="E7" s="51" t="n"/>
+      <c r="F7" s="51" t="n"/>
+      <c r="G7" s="50" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="43" t="inlineStr">
@@ -2074,7 +2024,6 @@
       <c r="E12" s="43" t="n"/>
       <c r="F12" s="43" t="n"/>
       <c r="G12" s="43" t="n"/>
-      <c r="H12" s="48" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="43" t="inlineStr">
@@ -2100,7 +2049,6 @@
       <c r="E13" s="43" t="n"/>
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="43" t="n"/>
-      <c r="H13" s="48" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="43" t="inlineStr">
@@ -2126,7 +2074,6 @@
       <c r="E14" s="43" t="n"/>
       <c r="F14" s="43" t="n"/>
       <c r="G14" s="43" t="n"/>
-      <c r="H14" s="48" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="43" t="inlineStr">
@@ -2152,7 +2099,6 @@
       <c r="E15" s="43" t="n"/>
       <c r="F15" s="43" t="n"/>
       <c r="G15" s="43" t="n"/>
-      <c r="H15" s="48" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="43" t="inlineStr">
@@ -2178,7 +2124,6 @@
       <c r="E16" s="43" t="n"/>
       <c r="F16" s="43" t="n"/>
       <c r="G16" s="43" t="n"/>
-      <c r="H16" s="48" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="43" t="inlineStr">
@@ -2204,7 +2149,6 @@
       <c r="E17" s="43" t="n"/>
       <c r="F17" s="43" t="n"/>
       <c r="G17" s="43" t="n"/>
-      <c r="H17" s="48" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2224,7 +2168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H14"/>
+  <dimension ref="A3:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2234,7 +2178,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -2248,12 +2191,11 @@
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="41" t="n"/>
-      <c r="D3" s="41" t="n"/>
-      <c r="E3" s="41" t="n"/>
-      <c r="F3" s="41" t="n"/>
-      <c r="G3" s="41" t="n"/>
-      <c r="H3" s="41" t="n"/>
+      <c r="C3" s="51" t="n"/>
+      <c r="D3" s="51" t="n"/>
+      <c r="E3" s="51" t="n"/>
+      <c r="F3" s="51" t="n"/>
+      <c r="G3" s="50" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="42" t="inlineStr">
@@ -2266,12 +2208,11 @@
           <t>TurnController</t>
         </is>
       </c>
-      <c r="C4" s="41" t="n"/>
-      <c r="D4" s="41" t="n"/>
-      <c r="E4" s="41" t="n"/>
-      <c r="F4" s="41" t="n"/>
-      <c r="G4" s="41" t="n"/>
-      <c r="H4" s="41" t="n"/>
+      <c r="C4" s="51" t="n"/>
+      <c r="D4" s="51" t="n"/>
+      <c r="E4" s="51" t="n"/>
+      <c r="F4" s="51" t="n"/>
+      <c r="G4" s="50" t="n"/>
     </row>
     <row r="5" ht="35.4" customHeight="1">
       <c r="A5" s="42" t="inlineStr">
@@ -2284,12 +2225,11 @@
           <t>Window 11, java version "1.8.0_503" , Junit 5</t>
         </is>
       </c>
-      <c r="C5" s="41" t="n"/>
-      <c r="D5" s="41" t="n"/>
-      <c r="E5" s="41" t="n"/>
-      <c r="F5" s="41" t="n"/>
-      <c r="G5" s="41" t="n"/>
-      <c r="H5" s="41" t="n"/>
+      <c r="C5" s="51" t="n"/>
+      <c r="D5" s="51" t="n"/>
+      <c r="E5" s="51" t="n"/>
+      <c r="F5" s="51" t="n"/>
+      <c r="G5" s="50" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="42" t="inlineStr">
@@ -2300,12 +2240,11 @@
       <c r="B6" s="45" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="41" t="n"/>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="41" t="n"/>
-      <c r="F6" s="41" t="n"/>
-      <c r="G6" s="41" t="n"/>
-      <c r="H6" s="41" t="n"/>
+      <c r="C6" s="51" t="n"/>
+      <c r="D6" s="51" t="n"/>
+      <c r="E6" s="51" t="n"/>
+      <c r="F6" s="51" t="n"/>
+      <c r="G6" s="50" t="n"/>
     </row>
     <row r="7" ht="35.4" customHeight="1">
       <c r="A7" s="42" t="inlineStr">
@@ -2318,12 +2257,11 @@
           <t>Mock TurnActionService, TurnService; direct method calls</t>
         </is>
       </c>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="41" t="n"/>
-      <c r="F7" s="41" t="n"/>
-      <c r="G7" s="41" t="n"/>
-      <c r="H7" s="41" t="n"/>
+      <c r="C7" s="51" t="n"/>
+      <c r="D7" s="51" t="n"/>
+      <c r="E7" s="51" t="n"/>
+      <c r="F7" s="51" t="n"/>
+      <c r="G7" s="50" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="43" t="inlineStr">
@@ -2386,7 +2324,6 @@
       <c r="E12" s="43" t="n"/>
       <c r="F12" s="43" t="n"/>
       <c r="G12" s="43" t="n"/>
-      <c r="H12" s="48" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="43" t="inlineStr">
@@ -2412,7 +2349,6 @@
       <c r="E13" s="43" t="n"/>
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="43" t="n"/>
-      <c r="H13" s="48" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="43" t="inlineStr">
@@ -2438,11 +2374,6 @@
       <c r="E14" s="43" t="n"/>
       <c r="F14" s="43" t="n"/>
       <c r="G14" s="43" t="n"/>
-      <c r="H14" s="48" t="inlineStr">
-        <is>
-          <t>check TurnController for the resolve endpoint - not covered yet</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2462,7 +2393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H13"/>
+  <dimension ref="A3:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2472,7 +2403,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -2486,12 +2416,11 @@
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="41" t="n"/>
-      <c r="D3" s="41" t="n"/>
-      <c r="E3" s="41" t="n"/>
-      <c r="F3" s="41" t="n"/>
-      <c r="G3" s="41" t="n"/>
-      <c r="H3" s="41" t="n"/>
+      <c r="C3" s="51" t="n"/>
+      <c r="D3" s="51" t="n"/>
+      <c r="E3" s="51" t="n"/>
+      <c r="F3" s="51" t="n"/>
+      <c r="G3" s="50" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="44" t="inlineStr">
@@ -2504,12 +2433,11 @@
           <t>PlayerController</t>
         </is>
       </c>
-      <c r="C4" s="41" t="n"/>
-      <c r="D4" s="41" t="n"/>
-      <c r="E4" s="41" t="n"/>
-      <c r="F4" s="41" t="n"/>
-      <c r="G4" s="41" t="n"/>
-      <c r="H4" s="41" t="n"/>
+      <c r="C4" s="51" t="n"/>
+      <c r="D4" s="51" t="n"/>
+      <c r="E4" s="51" t="n"/>
+      <c r="F4" s="51" t="n"/>
+      <c r="G4" s="50" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="44" t="inlineStr">
@@ -2522,12 +2450,11 @@
           <t>Window 11, java version "1.8.0_503" , Junit 5</t>
         </is>
       </c>
-      <c r="C5" s="41" t="n"/>
-      <c r="D5" s="41" t="n"/>
-      <c r="E5" s="41" t="n"/>
-      <c r="F5" s="41" t="n"/>
-      <c r="G5" s="41" t="n"/>
-      <c r="H5" s="41" t="n"/>
+      <c r="C5" s="51" t="n"/>
+      <c r="D5" s="51" t="n"/>
+      <c r="E5" s="51" t="n"/>
+      <c r="F5" s="51" t="n"/>
+      <c r="G5" s="50" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="44" t="inlineStr">
@@ -2538,12 +2465,11 @@
       <c r="B6" s="49" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="41" t="n"/>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="41" t="n"/>
-      <c r="F6" s="41" t="n"/>
-      <c r="G6" s="41" t="n"/>
-      <c r="H6" s="41" t="n"/>
+      <c r="C6" s="51" t="n"/>
+      <c r="D6" s="51" t="n"/>
+      <c r="E6" s="51" t="n"/>
+      <c r="F6" s="51" t="n"/>
+      <c r="G6" s="50" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="44" t="inlineStr">
@@ -2556,12 +2482,11 @@
           <t>MockMvc / mock PlayerService, GameViewService</t>
         </is>
       </c>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="41" t="n"/>
-      <c r="F7" s="41" t="n"/>
-      <c r="G7" s="41" t="n"/>
-      <c r="H7" s="41" t="n"/>
+      <c r="C7" s="51" t="n"/>
+      <c r="D7" s="51" t="n"/>
+      <c r="E7" s="51" t="n"/>
+      <c r="F7" s="51" t="n"/>
+      <c r="G7" s="50" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="43" t="inlineStr">
@@ -2624,11 +2549,6 @@
       <c r="E12" s="43" t="n"/>
       <c r="F12" s="43" t="n"/>
       <c r="G12" s="43" t="n"/>
-      <c r="H12" s="48" t="inlineStr">
-        <is>
-          <t>covered by GameEndpointTest</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="43" t="inlineStr">
@@ -2654,7 +2574,6 @@
       <c r="E13" s="43" t="n"/>
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="43" t="n"/>
-      <c r="H13" s="48" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2674,7 +2593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H15"/>
+  <dimension ref="A3:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2684,7 +2603,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -2698,12 +2616,11 @@
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="41" t="n"/>
-      <c r="D3" s="41" t="n"/>
-      <c r="E3" s="41" t="n"/>
-      <c r="F3" s="41" t="n"/>
-      <c r="G3" s="41" t="n"/>
-      <c r="H3" s="41" t="n"/>
+      <c r="C3" s="51" t="n"/>
+      <c r="D3" s="51" t="n"/>
+      <c r="E3" s="51" t="n"/>
+      <c r="F3" s="51" t="n"/>
+      <c r="G3" s="50" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="44" t="inlineStr">
@@ -2716,12 +2633,11 @@
           <t>MarshalDraftController</t>
         </is>
       </c>
-      <c r="C4" s="41" t="n"/>
-      <c r="D4" s="41" t="n"/>
-      <c r="E4" s="41" t="n"/>
-      <c r="F4" s="41" t="n"/>
-      <c r="G4" s="41" t="n"/>
-      <c r="H4" s="41" t="n"/>
+      <c r="C4" s="51" t="n"/>
+      <c r="D4" s="51" t="n"/>
+      <c r="E4" s="51" t="n"/>
+      <c r="F4" s="51" t="n"/>
+      <c r="G4" s="50" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="44" t="inlineStr">
@@ -2734,12 +2650,11 @@
           <t>Window 11, java version "1.8.0_503" , Junit 5</t>
         </is>
       </c>
-      <c r="C5" s="41" t="n"/>
-      <c r="D5" s="41" t="n"/>
-      <c r="E5" s="41" t="n"/>
-      <c r="F5" s="41" t="n"/>
-      <c r="G5" s="41" t="n"/>
-      <c r="H5" s="41" t="n"/>
+      <c r="C5" s="51" t="n"/>
+      <c r="D5" s="51" t="n"/>
+      <c r="E5" s="51" t="n"/>
+      <c r="F5" s="51" t="n"/>
+      <c r="G5" s="50" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="44" t="inlineStr">
@@ -2750,12 +2665,11 @@
       <c r="B6" s="49" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="41" t="n"/>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="41" t="n"/>
-      <c r="F6" s="41" t="n"/>
-      <c r="G6" s="41" t="n"/>
-      <c r="H6" s="41" t="n"/>
+      <c r="C6" s="51" t="n"/>
+      <c r="D6" s="51" t="n"/>
+      <c r="E6" s="51" t="n"/>
+      <c r="F6" s="51" t="n"/>
+      <c r="G6" s="50" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="44" t="inlineStr">
@@ -2768,12 +2682,11 @@
           <t>MockMvc / MarshalCandidateService, MarshalDraftService</t>
         </is>
       </c>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="41" t="n"/>
-      <c r="F7" s="41" t="n"/>
-      <c r="G7" s="41" t="n"/>
-      <c r="H7" s="41" t="n"/>
+      <c r="C7" s="51" t="n"/>
+      <c r="D7" s="51" t="n"/>
+      <c r="E7" s="51" t="n"/>
+      <c r="F7" s="51" t="n"/>
+      <c r="G7" s="50" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="43" t="inlineStr">
@@ -2836,11 +2749,6 @@
       <c r="E12" s="43" t="n"/>
       <c r="F12" s="43" t="n"/>
       <c r="G12" s="43" t="n"/>
-      <c r="H12" s="48" t="inlineStr">
-        <is>
-          <t>covered by GameEndpointTest</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="43" t="inlineStr">
@@ -2866,11 +2774,6 @@
       <c r="E13" s="43" t="n"/>
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="43" t="n"/>
-      <c r="H13" s="48" t="inlineStr">
-        <is>
-          <t>MarshalDraftController.java:20</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="43" t="inlineStr">
@@ -2896,11 +2799,6 @@
       <c r="E14" s="43" t="n"/>
       <c r="F14" s="43" t="n"/>
       <c r="G14" s="43" t="n"/>
-      <c r="H14" s="48" t="inlineStr">
-        <is>
-          <t>MarshalDraftController.java:31</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="43" t="inlineStr">
@@ -2926,7 +2824,6 @@
       <c r="E15" s="43" t="n"/>
       <c r="F15" s="43" t="n"/>
       <c r="G15" s="43" t="n"/>
-      <c r="H15" s="48" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2946,7 +2843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H13"/>
+  <dimension ref="A3:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2956,7 +2853,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -2970,12 +2866,11 @@
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="41" t="n"/>
-      <c r="D3" s="41" t="n"/>
-      <c r="E3" s="41" t="n"/>
-      <c r="F3" s="41" t="n"/>
-      <c r="G3" s="41" t="n"/>
-      <c r="H3" s="41" t="n"/>
+      <c r="C3" s="51" t="n"/>
+      <c r="D3" s="51" t="n"/>
+      <c r="E3" s="51" t="n"/>
+      <c r="F3" s="51" t="n"/>
+      <c r="G3" s="50" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="44" t="inlineStr">
@@ -2988,12 +2883,11 @@
           <t>PlacementController</t>
         </is>
       </c>
-      <c r="C4" s="41" t="n"/>
-      <c r="D4" s="41" t="n"/>
-      <c r="E4" s="41" t="n"/>
-      <c r="F4" s="41" t="n"/>
-      <c r="G4" s="41" t="n"/>
-      <c r="H4" s="41" t="n"/>
+      <c r="C4" s="51" t="n"/>
+      <c r="D4" s="51" t="n"/>
+      <c r="E4" s="51" t="n"/>
+      <c r="F4" s="51" t="n"/>
+      <c r="G4" s="50" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="44" t="inlineStr">
@@ -3006,12 +2900,11 @@
           <t>Window 11, java version "1.8.0_503" , Junit 5</t>
         </is>
       </c>
-      <c r="C5" s="41" t="n"/>
-      <c r="D5" s="41" t="n"/>
-      <c r="E5" s="41" t="n"/>
-      <c r="F5" s="41" t="n"/>
-      <c r="G5" s="41" t="n"/>
-      <c r="H5" s="41" t="n"/>
+      <c r="C5" s="51" t="n"/>
+      <c r="D5" s="51" t="n"/>
+      <c r="E5" s="51" t="n"/>
+      <c r="F5" s="51" t="n"/>
+      <c r="G5" s="50" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="44" t="inlineStr">
@@ -3022,12 +2915,11 @@
       <c r="B6" s="49" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="41" t="n"/>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="41" t="n"/>
-      <c r="F6" s="41" t="n"/>
-      <c r="G6" s="41" t="n"/>
-      <c r="H6" s="41" t="n"/>
+      <c r="C6" s="51" t="n"/>
+      <c r="D6" s="51" t="n"/>
+      <c r="E6" s="51" t="n"/>
+      <c r="F6" s="51" t="n"/>
+      <c r="G6" s="50" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="44" t="inlineStr">
@@ -3040,12 +2932,11 @@
           <t>MockMvc / PlacementService</t>
         </is>
       </c>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="41" t="n"/>
-      <c r="F7" s="41" t="n"/>
-      <c r="G7" s="41" t="n"/>
-      <c r="H7" s="41" t="n"/>
+      <c r="C7" s="51" t="n"/>
+      <c r="D7" s="51" t="n"/>
+      <c r="E7" s="51" t="n"/>
+      <c r="F7" s="51" t="n"/>
+      <c r="G7" s="50" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="43" t="inlineStr">
@@ -3108,11 +2999,6 @@
       <c r="E12" s="43" t="n"/>
       <c r="F12" s="43" t="n"/>
       <c r="G12" s="43" t="n"/>
-      <c r="H12" s="48" t="inlineStr">
-        <is>
-          <t>PlacementController.java:15</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="43" t="inlineStr">
@@ -3138,7 +3024,6 @@
       <c r="E13" s="43" t="n"/>
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="43" t="n"/>
-      <c r="H13" s="48" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3158,7 +3043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H13"/>
+  <dimension ref="A3:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3168,7 +3053,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -3182,12 +3066,11 @@
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="41" t="n"/>
-      <c r="D3" s="41" t="n"/>
-      <c r="E3" s="41" t="n"/>
-      <c r="F3" s="41" t="n"/>
-      <c r="G3" s="41" t="n"/>
-      <c r="H3" s="41" t="n"/>
+      <c r="C3" s="51" t="n"/>
+      <c r="D3" s="51" t="n"/>
+      <c r="E3" s="51" t="n"/>
+      <c r="F3" s="51" t="n"/>
+      <c r="G3" s="50" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="44" t="inlineStr">
@@ -3200,12 +3083,11 @@
           <t>GameLogController</t>
         </is>
       </c>
-      <c r="C4" s="41" t="n"/>
-      <c r="D4" s="41" t="n"/>
-      <c r="E4" s="41" t="n"/>
-      <c r="F4" s="41" t="n"/>
-      <c r="G4" s="41" t="n"/>
-      <c r="H4" s="41" t="n"/>
+      <c r="C4" s="51" t="n"/>
+      <c r="D4" s="51" t="n"/>
+      <c r="E4" s="51" t="n"/>
+      <c r="F4" s="51" t="n"/>
+      <c r="G4" s="50" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="44" t="inlineStr">
@@ -3218,12 +3100,11 @@
           <t>Window 11, java version "1.8.0_503" , Junit 5</t>
         </is>
       </c>
-      <c r="C5" s="41" t="n"/>
-      <c r="D5" s="41" t="n"/>
-      <c r="E5" s="41" t="n"/>
-      <c r="F5" s="41" t="n"/>
-      <c r="G5" s="41" t="n"/>
-      <c r="H5" s="41" t="n"/>
+      <c r="C5" s="51" t="n"/>
+      <c r="D5" s="51" t="n"/>
+      <c r="E5" s="51" t="n"/>
+      <c r="F5" s="51" t="n"/>
+      <c r="G5" s="50" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="44" t="inlineStr">
@@ -3234,12 +3115,11 @@
       <c r="B6" s="49" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="41" t="n"/>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="41" t="n"/>
-      <c r="F6" s="41" t="n"/>
-      <c r="G6" s="41" t="n"/>
-      <c r="H6" s="41" t="n"/>
+      <c r="C6" s="51" t="n"/>
+      <c r="D6" s="51" t="n"/>
+      <c r="E6" s="51" t="n"/>
+      <c r="F6" s="51" t="n"/>
+      <c r="G6" s="50" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="44" t="inlineStr">
@@ -3252,12 +3132,11 @@
           <t>MockMvc / BattleService, GameEventService</t>
         </is>
       </c>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="41" t="n"/>
-      <c r="F7" s="41" t="n"/>
-      <c r="G7" s="41" t="n"/>
-      <c r="H7" s="41" t="n"/>
+      <c r="C7" s="51" t="n"/>
+      <c r="D7" s="51" t="n"/>
+      <c r="E7" s="51" t="n"/>
+      <c r="F7" s="51" t="n"/>
+      <c r="G7" s="50" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="43" t="inlineStr">
@@ -3320,11 +3199,6 @@
       <c r="E12" s="43" t="n"/>
       <c r="F12" s="43" t="n"/>
       <c r="G12" s="43" t="n"/>
-      <c r="H12" s="48" t="inlineStr">
-        <is>
-          <t>covered by GameEndpointTest</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="43" t="inlineStr">
@@ -3350,11 +3224,6 @@
       <c r="E13" s="43" t="n"/>
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="43" t="n"/>
-      <c r="H13" s="48" t="inlineStr">
-        <is>
-          <t>GameLogController.java:30</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
